--- a/backend/docs/elever Anes.xlsx
+++ b/backend/docs/elever Anes.xlsx
@@ -304,7 +304,7 @@
     <t xml:space="preserve">19820924-0608</t>
   </si>
   <si>
-    <t xml:space="preserve">Administration - påbyggnad marknadsassistent</t>
+    <t xml:space="preserve">Administration, påbyggnad marknadsassistent</t>
   </si>
   <si>
     <t xml:space="preserve">Järfälla</t>
@@ -528,24 +528,28 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -801,770 +805,770 @@
   <dimension ref="A1:J25"/>
   <sheetFormatPr defaultColWidth="8.75390625" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="10.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="39.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="31.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="10.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="20.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="39.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="16.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="12.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="31.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="12.22"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="4" t="n">
+      <c r="C2" s="5" t="n">
         <v>45698</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="5" t="n">
         <v>45870</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C3" s="5" t="n">
         <v>45698</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="5" t="n">
         <v>45870</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="5" t="n">
         <v>45698</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="5" t="n">
         <v>45870</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="4" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="5" t="n">
         <v>45698</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="5" t="n">
         <v>45870</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="4" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="4" t="n">
-        <v>45873</v>
-      </c>
-      <c r="D6" s="4" t="n">
+      <c r="C6" s="5" t="n">
+        <v>45873</v>
+      </c>
+      <c r="D6" s="5" t="n">
         <v>45940</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="5" t="n">
         <v>45931</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="H6" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="I6" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="J6" s="3"/>
+      <c r="J6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="4" t="n">
-        <v>45873</v>
-      </c>
-      <c r="D7" s="4" t="n">
+      <c r="C7" s="5" t="n">
+        <v>45873</v>
+      </c>
+      <c r="D7" s="5" t="n">
         <v>45940</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="5" t="n">
         <v>45931</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H7" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="I7" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="J7" s="4" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C8" s="4" t="n">
-        <v>45873</v>
-      </c>
-      <c r="D8" s="4" t="n">
+      <c r="C8" s="5" t="n">
+        <v>45873</v>
+      </c>
+      <c r="D8" s="5" t="n">
         <v>45940</v>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" s="5" t="n">
         <v>45931</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="H8" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="I8" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="J8" s="3"/>
+      <c r="J8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="4" t="n">
-        <v>45873</v>
-      </c>
-      <c r="D9" s="4" t="n">
+      <c r="C9" s="5" t="n">
+        <v>45873</v>
+      </c>
+      <c r="D9" s="5" t="n">
         <v>45940</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" s="5" t="n">
         <v>45931</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="H9" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="I9" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="J9" s="3"/>
+      <c r="J9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C10" s="4" t="n">
-        <v>45873</v>
-      </c>
-      <c r="D10" s="4" t="n">
+      <c r="C10" s="5" t="n">
+        <v>45873</v>
+      </c>
+      <c r="D10" s="5" t="n">
         <v>45940</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" s="5" t="n">
         <v>45931</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="H10" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="I10" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="J10" s="3"/>
+      <c r="J10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C11" s="4" t="n">
-        <v>45873</v>
-      </c>
-      <c r="D11" s="4" t="n">
+      <c r="C11" s="5" t="n">
+        <v>45873</v>
+      </c>
+      <c r="D11" s="5" t="n">
         <v>45940</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" s="5" t="n">
         <v>45931</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="H11" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="I11" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="J11" s="3"/>
+      <c r="J11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C12" s="4" t="n">
-        <v>45873</v>
-      </c>
-      <c r="D12" s="4" t="n">
+      <c r="C12" s="5" t="n">
+        <v>45873</v>
+      </c>
+      <c r="D12" s="5" t="n">
         <v>45940</v>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="E12" s="5" t="n">
         <v>45931</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="G12" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="H12" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="I12" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="J12" s="3"/>
+      <c r="J12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="4" t="n">
-        <v>45873</v>
-      </c>
-      <c r="D13" s="4" t="n">
+      <c r="C13" s="5" t="n">
+        <v>45873</v>
+      </c>
+      <c r="D13" s="5" t="n">
         <v>46010</v>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E13" s="5" t="n">
         <v>46001</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="G13" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="H13" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="I13" s="3" t="s">
+      <c r="I13" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="J13" s="3"/>
+      <c r="J13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C14" s="4" t="n">
-        <v>45873</v>
-      </c>
-      <c r="D14" s="4" t="n">
+      <c r="C14" s="5" t="n">
+        <v>45873</v>
+      </c>
+      <c r="D14" s="5" t="n">
         <v>45940</v>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="E14" s="5" t="n">
         <v>45931</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="G14" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="H14" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="I14" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="J14" s="3"/>
+      <c r="J14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="4" t="n">
-        <v>45873</v>
-      </c>
-      <c r="D15" s="4" t="n">
+      <c r="C15" s="5" t="n">
+        <v>45873</v>
+      </c>
+      <c r="D15" s="5" t="n">
         <v>45940</v>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="E15" s="5" t="n">
         <v>45931</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="F15" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="G15" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="H15" s="3" t="s">
+      <c r="H15" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="I15" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="J15" s="3" t="s">
+      <c r="J15" s="4" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="C16" s="4" t="n">
-        <v>45873</v>
-      </c>
-      <c r="D16" s="4" t="n">
+      <c r="C16" s="5" t="n">
+        <v>45873</v>
+      </c>
+      <c r="D16" s="5" t="n">
         <v>45940</v>
       </c>
-      <c r="E16" s="4" t="n">
+      <c r="E16" s="5" t="n">
         <v>45931</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="F16" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="G16" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="H16" s="3" t="s">
+      <c r="H16" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="I16" s="3" t="s">
+      <c r="I16" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="J16" s="3"/>
+      <c r="J16" s="4"/>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="C17" s="4" t="n">
-        <v>45873</v>
-      </c>
-      <c r="D17" s="4" t="n">
+      <c r="C17" s="5" t="n">
+        <v>45873</v>
+      </c>
+      <c r="D17" s="5" t="n">
         <v>46010</v>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E17" s="5" t="n">
         <v>46001</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F17" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="G17" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="H17" s="3" t="s">
+      <c r="H17" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="I17" s="3" t="s">
+      <c r="I17" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="J17" s="3"/>
+      <c r="J17" s="4"/>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="C18" s="4" t="n">
-        <v>45873</v>
-      </c>
-      <c r="D18" s="4" t="n">
+      <c r="C18" s="5" t="n">
+        <v>45873</v>
+      </c>
+      <c r="D18" s="5" t="n">
         <v>46010</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E18" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="F18" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="G18" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="H18" s="3" t="s">
+      <c r="H18" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="I18" s="3" t="s">
+      <c r="I18" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="J18" s="3"/>
+      <c r="J18" s="4"/>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C19" s="4" t="n">
-        <v>45873</v>
-      </c>
-      <c r="D19" s="4" t="n">
+      <c r="C19" s="5" t="n">
+        <v>45873</v>
+      </c>
+      <c r="D19" s="5" t="n">
         <v>46045</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="F19" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="G19" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H19" s="3" t="s">
+      <c r="H19" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="I19" s="3" t="s">
+      <c r="I19" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="J19" s="3"/>
+      <c r="J19" s="4"/>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="C20" s="4" t="n">
-        <v>45873</v>
-      </c>
-      <c r="D20" s="4" t="n">
+      <c r="C20" s="5" t="n">
+        <v>45873</v>
+      </c>
+      <c r="D20" s="5" t="n">
         <v>46045</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E20" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="F20" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="G20" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="H20" s="3" t="s">
+      <c r="H20" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="I20" s="3" t="s">
+      <c r="I20" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="J20" s="3" t="s">
+      <c r="J20" s="4" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C21" s="4" t="n">
-        <v>45873</v>
-      </c>
-      <c r="D21" s="4" t="n">
+      <c r="C21" s="5" t="n">
+        <v>45873</v>
+      </c>
+      <c r="D21" s="5" t="n">
         <v>46045</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E21" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="F21" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="G21" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="H21" s="3" t="s">
+      <c r="H21" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="I21" s="3" t="s">
+      <c r="I21" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="J21" s="3"/>
+      <c r="J21" s="4"/>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="C22" s="4" t="n">
-        <v>45873</v>
-      </c>
-      <c r="D22" s="4" t="n">
+      <c r="C22" s="5" t="n">
+        <v>45873</v>
+      </c>
+      <c r="D22" s="5" t="n">
         <v>46045</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="E22" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="F22" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="G22" s="3" t="s">
+      <c r="G22" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="H22" s="3" t="s">
+      <c r="H22" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="I22" s="3" t="s">
+      <c r="I22" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="J22" s="3"/>
+      <c r="J22" s="4"/>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="C23" s="4" t="n">
-        <v>45873</v>
-      </c>
-      <c r="D23" s="4" t="n">
+      <c r="C23" s="5" t="n">
+        <v>45873</v>
+      </c>
+      <c r="D23" s="5" t="n">
         <v>46045</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="E23" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="F23" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="G23" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="H23" s="3" t="s">
+      <c r="H23" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="I23" s="3" t="s">
+      <c r="I23" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="J23" s="3"/>
+      <c r="J23" s="4"/>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="C24" s="4" t="n">
-        <v>45873</v>
-      </c>
-      <c r="D24" s="4" t="n">
+      <c r="C24" s="5" t="n">
+        <v>45873</v>
+      </c>
+      <c r="D24" s="5" t="n">
         <v>46185</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="E24" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="F24" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="G24" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="H24" s="3" t="s">
+      <c r="H24" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="I24" s="3" t="s">
+      <c r="I24" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="J24" s="3"/>
+      <c r="J24" s="4"/>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="C25" s="4" t="n">
-        <v>45873</v>
-      </c>
-      <c r="D25" s="4" t="n">
+      <c r="C25" s="5" t="n">
+        <v>45873</v>
+      </c>
+      <c r="D25" s="5" t="n">
         <v>46185</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="E25" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="F25" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="G25" s="3" t="s">
+      <c r="G25" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="H25" s="3" t="s">
+      <c r="H25" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="I25" s="3" t="s">
+      <c r="I25" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="J25" s="3" t="s">
+      <c r="J25" s="4" t="s">
         <v>43</v>
       </c>
     </row>

--- a/backend/docs/elever Anes.xlsx
+++ b/backend/docs/elever Anes.xlsx
@@ -807,7 +807,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32.12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="10.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="12.8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="20.69"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="39.44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="16.55"/>
